--- a/Анализ_ГК_АГАТ_LADA_Автопрофиль_Август_Сентябрь_2026.xlsx
+++ b/Анализ_ГК_АГАТ_LADA_Автопрофиль_Август_Сентябрь_2026.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,11 +214,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -251,6 +251,8 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -640,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1073,7 +1075,7 @@
     <row r="22">
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Всего входящих лидов LADA в CRM (Новый лид)</t>
+          <t>1. Общий входящий спрос клиентов в регионе НН +200 км (Новый лид)</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
@@ -1095,14 +1097,14 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Стабильно высокий общий спрос на LADA в регионе НН +200 км</t>
+          <t>Стабильно высокий спрос покупателей из Нижегородского региона</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Квалифицированные лиды CRM (Закрепление менеджера)</t>
+          <t>2. Квалифицированные клиенты региона (Закрепление менеджера)</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
@@ -1129,167 +1131,167 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Всего передано дилерам в НН +200 км (все каналы)</t>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>3. ПЕРЕДАНО ЛОКАЛЬНЫМ ДИЛЕРАМ В РАДИУСЕ 200 КМ (ФАКТ)</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>527.8</v>
+        <v>700</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Взрывной рост передачи лидов в дилерскую сеть в сентябре</t>
+          <t>Физические официальные дилерские центры LADA в регионе (АГАТ + ЮНИКОР)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Передано конкуренту: ЮНИКОР Дзержинск</t>
+          <t xml:space="preserve">  • ГК АГАТ (ЮЛ «Автопрофиль», CRM + MAX)</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>577.8</v>
+        <v>2100</v>
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>ЮНИКОР забирает свыше половины всего переданного потока сети!</t>
+          <t>Нижний Новгород (Московское ш., Родионова) — абсолютный лидер региона!</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Передано АГАТ (Автопрофиль, CRM + MAX)</t>
+          <t xml:space="preserve">  • ЮНИКОР Дзержинск (пр-кт Чкалова / НН)</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2100</v>
+        <v>233.3</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2 лида через CRM-кнопку + 20 обращений через рабочий чат MAX</t>
+          <t>Дзержинск (33 км от НН) — 10 уникальных передач (официальный BI СберАвто)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Передано другим партнерам / удаленным ДЦ</t>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>4. УТЕЧКА КЛИЕНТОВ ЗА ПРЕДЕЛЫ 200 КМ (Удаленные кредитные хабы / ФДЦ)</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>275</v>
+        <v>-111</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-86.7</v>
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Техно-Темп, Кан-Авто, Р-Моторс (клиенты с номерами НН)</t>
+          <t>Нижегородские онлайн-заявки, направленные операторами в удаленные центры</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>ДОЛЯ АГАТ от переданного трафика в НН +200 км</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>248.2</v>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • ФДЦ Техно-Темп (Краснодар, ~1 400 км от НН)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>-81</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>-87.09999999999999</v>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Доля АГАТ выросла с 5.6% до 19.5% исключительно за счет чата MAX</t>
+          <t>Удаленный кредитный шлюз СберАвто для онлайн-заявок на автокредит</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>ДОЛЯ АГАТ от квалифицированного спроса региона</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>2633.3</v>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • ФДЦ Р-Моторс (удаленный кредитный пилот)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-71.40000000000001</v>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
@@ -1298,401 +1300,575 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>АГАТ получает менее 10% от доступных покупателей LADA в НН!</t>
+          <t>Удаленный пилот обработки кредитных сделок СберАвто</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Релевантный трафик, НЕ полученный АГАТ (потенциал)</t>
+          <t xml:space="preserve">  • КАН АВТО (Казань, ~400 км от НН)</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>302</v>
+        <v>1</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>-18.2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>247 готовых покупателей LADA ушли мимо АГАТ за 25 дней сентября</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+          <t>Заявки клиентов восточных районов области</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Прочие удаленные ДЦ (Боравто Воронеж и др.)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>В августе уходило в Боравто (8), Р-Моторс (7) и др.; в сентябре утечка перекрыта</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>5. НЕ ПЕРЕДАНО ДИЛЕРАМ ОТ ВХОДЯЩИХ ЛИДОВ (баланс: 230 - 49)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>181</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>78.7%</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Остаток входящего спроса без передачи в ДЦ (баланс: 49 передано + 181 = 230)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • в т.ч. квалифицированные клиенты без передачи (269 - 49)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Целевой резерв из прошедших скоринг клиентов (баланс: 49 + 220 = 269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ДОЛЯ АГАТ СРЕДИ ЛОКАЛЬНЫХ ДИЛЕРОВ (АГАТ vs ЮНИКОР)</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Среди дилеров области АГАТ забирает 68.8% (22 из 32), опережая ЮНИКОР в 2.2 раза!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>ДОЛЯ АГАТ ОТ ВСЕХ ПЕРЕДАННЫХ КЛИЕНТОВ РЕГИОНА (с учетом утечки)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>5512.5</v>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>44.9%</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Доля АГАТ во всех передачах нижегородцев выросла с 0.8% до 44.9%!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>ДОЛЯ АГАТ ОТ КВАЛИФИЦИРОВАННОГО СПРОСА РЕГИОНА (269 лидов)</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>2633.3</v>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Потенциал роста доли АГАТ — минимум в 3–4 раза (до 30–40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>БЛОК 3. АНАЛИЗ ЧАТА MAX («СБЕРАВТО&amp;АГАТ НН ЛАДА(АВТОПРОФИЛЬ)»)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Показатель обработки переписки MAX</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>% от переданных</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Бенчмарк сети</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Статус / Оценка</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Выделено тематических цепочек по клиентам</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Базовый объем обращений за 1–25 сентября</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Уникальных клиентских кейсов (нижняя граница)</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>2 цепочки могут быть повторными из-за отсутствия ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Подтвержденных выдач автомобилей в чате</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>12.9%</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Зафиксированы в чате (Vesta Comfort, Granta x2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Случаи с внесенным авансом (ожидание выдачи)</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>8.0%</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Внесен аванс (Granta Comfort черный, Granta)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Явные отказы клиентов (зафиксированные)</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Трейд-ин BMW на Largus: разногласие по доплате</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="21" t="inlineStr">
-        <is>
-          <t>В работе / без зафиксированного итога в чате</t>
-        </is>
-      </c>
-      <c r="C39" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>&lt; 35.0%</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>КРИТИЧЕСКАЯ ЗОНА: по 14 лидам дилер не дал финал!</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Ценовые расхождения (эпизоды в чате)</t>
+          <t>Выделено тематических цепочек по клиентам</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Ни одно не привело к окончательному отказу</t>
+          <t>Базовый объем обращений за 1–25 сентября</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Потери из-за ожидания в салоне (&gt;1.5 часа)</t>
+          <t>Уникальных клиентских кейсов (нижняя граница)</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2 цепочки могут быть повторными из-за отсутствия ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Подтвержденных выдач автомобилей в чате</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Зафиксированы в чате (Vesta Comfort, Granta x2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Случаи с внесенным авансом (ожидание выдачи)</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Внесен аванс (Granta Comfort черный, Granta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Явные отказы клиентов (зафиксированные)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>5.0%</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>23.09 клиент ждал кредитного специалиста 1.5ч в ДЦ</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>БЛОК 4. СВЕРКА MAX VS DASHBOARD СБЕРАВТО</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Категория сверки</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Кол-во клиентов</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Характер расхождения</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Управленческий риск / Решение</t>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Трейд-ин BMW на Largus: разногласие по доплате</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Сделка есть в Dashboard, но нет выдачи в MAX</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>В Dashboard закрыто 9 сделок, а в чате MAX подтверждено только 3 выдачи</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Дилер закрывает сделки, но не отчитывается в чате. Риск потери контроля воронки</t>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>В работе / без зафиксированного итога в чате</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>&lt; 35.0%</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>КРИТИЧЕСКАЯ ЗОНА: по 14 лидам дилер не дал финал!</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Сделка подтверждена в MAX и есть в Dashboard</t>
+          <t>Ценовые расхождения (эпизоды в чате)</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Полное совпадение факта выдачи автомобиля (100% верификация)</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>Успешные кейсы качественного взаимодействия СберАвто и АГАТ</t>
+        <v>4</v>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Ни одно не привело к окончательному отказу</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
         <is>
+          <t>Потери из-за ожидания в салоне (&gt;1.5 часа)</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>23.09 клиент ждал кредитного специалиста 1.5ч в ДЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>БЛОК 4. СВЕРКА MAX VS DASHBOARD СБЕРАВТО</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Категория сверки</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Кол-во клиентов</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Характер расхождения</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Управленческий риск / Решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>Сделка есть в Dashboard, но нет выдачи в MAX</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>В Dashboard закрыто 9 сделок, а в чате MAX подтверждено только 3 выдачи</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Дилер закрывает сделки, но не отчитывается в чате. Риск потери контроля воронки</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Сделка подтверждена в MAX и есть в Dashboard</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Полное совпадение факта выдачи автомобиля (100% верификация)</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Успешные кейсы качественного взаимодействия СберАвто и АГАТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
           <t>Внесен аванс в MAX, ожидается выдача в Dashboard</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
+      <c r="C53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Предоплаты отражены в чате, сделка в процессе подготовки</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Потенциал закрытия до конца месяца (дополнительно +2 продажи)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="8" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Зависли в статусе «В работе» в чате MAX</t>
         </is>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C54" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Нет финального статуса от дилера по запросам наличия и лидам</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Требуется срочный реестровый запрос в АГАТ по статусам каждого клиента</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="5" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Клиенты ушли конкуренту ЮНИКОР Дзержинск</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>61 лид передан ЮНИКОР из-за настроек автоматической маршрутизации</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>АГАТ недополучает до 50–60 целевых лидов в месяц из-за правил распределения</t>
+      <c r="C55" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>10 уникальных лидов передано ЮНИКОР (официальный BI СберАвто)</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>АГАТ опережает ЮНИКОР (22 vs 10), но ЮНИКОР остается системным получателем по умолчанию</t>
         </is>
       </c>
     </row>
@@ -1764,10 +1940,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>269 целевых клиентов</t>
         </is>
@@ -1784,30 +1960,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="36" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>61 лид конкуренту ЮНИКОР</t>
+          <t>10 лидов конкуренту ЮНИКОР</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Объем переданного трафика LADA партнеру ЮНИКОР Дзержинск в сентябре</t>
+          <t>Объем переданного трафика LADA партнеру ЮНИКОР Дзержинск в сентябре (официальный BI)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>ЮНИКОР забирает 54% всего трафика сети, АГАТ недополучает целевых покупателей</t>
+          <t>АГАТ опережает ЮНИКОР в 2.2 раза (22 лида vs 10), но ЮНИКОР сохраняет статус шлюза по умолчанию</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>9 продаж LADA Автопрофиль</t>
         </is>
@@ -1824,7 +2000,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="36" t="n">
         <v>4</v>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -1844,10 +2020,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>0 отказов по цене</t>
         </is>
@@ -1894,10 +2070,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>АГАТ получил только 22 обращения из 269 (8.2% рынка)</t>
         </is>
@@ -1914,30 +2090,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="36" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>ЮНИКОР вырос с 9 до 61 лида (+577%)</t>
+          <t>АГАТ опережает ЮНИКОР по лидам (22 vs 10)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Маршрутизация СберАвто перекошена в пользу Дзержинска из-за настроек шлюза</t>
+          <t>АГАТ является лидером по передачам в регионе, но получает их вручную через MAX</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Установить паритетное распределение 50/50 между АГАТ и ЮНИКОР по Нижегородской агломерации</t>
+          <t>Включить системную интеграцию и зафиксировать за АГАТ 70% трафика агломерации</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>В Dashboard 9 сделок, в MAX отчитались только по 3</t>
         </is>
@@ -1954,7 +2130,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="36" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -1974,10 +2150,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Зафиксирован простой клиента в ДЦ более 1.5 часов (кейс 23.09)</t>
         </is>
@@ -2029,12 +2205,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>СберАвто</t>
         </is>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2054,17 +2230,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>СберАвто</t>
         </is>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Скорректировать гео-маршрутизацию в радиусе 50 км (перенаправить поток Бора/Кстово/Балахны на АГАТ)</t>
+          <t>Скорректировать гео-маршрутизацию в радиусе 50 км (перенаправить поток Бора/Кстово/Балахны и кредитный шлюз на АГАТ)</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -2074,17 +2250,17 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Перераспределение до 30 качественных лидов от ЮНИКОР в АГАТ</t>
+          <t>Перераспределение до 20–30 качественных лидов дополнительно в АГАТ</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>СберАвто</t>
         </is>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="37" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2104,12 +2280,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>ГК АГАТ</t>
         </is>
       </c>
-      <c r="C26" s="34" t="n">
+      <c r="C26" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2129,12 +2305,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>ГК АГАТ</t>
         </is>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="37" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2154,12 +2330,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>ГК АГАТ</t>
         </is>
       </c>
-      <c r="C28" s="34" t="n">
+      <c r="C28" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2254,12 +2430,12 @@
           <t>Сентябрь содержит 25 дней против 31 дня полного августа</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Нельзя напрямую сравнивать валовые штуки</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>ВЫСОКАЯ (при MTD сравнении)</t>
         </is>
@@ -2281,12 +2457,12 @@
           <t>В договорах Автопрофиль — ЮЛ, а ДЦ — Московское ш. и Родионова</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Риск смешения ЮЛ и географической точки</t>
         </is>
       </c>
-      <c r="E7" s="40" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>ВЫСОКАЯ (правило соблюдено)</t>
         </is>
@@ -2308,12 +2484,12 @@
           <t>15 сделок сентября по Автопрофилю заведены как «Сделка без кнопки»</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Лиды не отражаются в колонке стандартных переданных лидов CRM</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>ВЫСОКАЯ (сверено с Bitrix)</t>
         </is>
@@ -2335,7 +2511,7 @@
           <t>2 из 20 цепочек в MAX не содержали явного Client ID</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Риск дублирования или задвоения обращений</t>
         </is>
@@ -2362,12 +2538,12 @@
           <t>В текстовых полях CRM встречается 'Новгородская область' (Великий Новгород)</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Риск попадания клиентов за 800 км от НН в радиус 200 км</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>ВЫСОКАЯ (очищено)</t>
         </is>
@@ -2389,12 +2565,12 @@
           <t>Правило проекта запрещает суммировать sys_db_partners и lead_geo_dealers</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Риск искусственного завышения трафика в 1.5–2 раза</t>
         </is>
       </c>
-      <c r="E11" s="40" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>ВЫСОКАЯ (правило соблюдено)</t>
         </is>
@@ -2416,12 +2592,12 @@
           <t>В чате MAX присутствуют фамилии клиентов и телефоны</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Требование п. 29 ТЗ по защите ПДн</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>ВЫСОКАЯ (ПДн удалены)</t>
         </is>
@@ -3645,7 +3821,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>УТЕЧКА 91.8%: трафик уходит в ЮНИКОР (61) и др. ДЦ</t>
+          <t>УТЕЧКА 91.8%: 220 клиентов не распределены дилерам, 17 ушли в кредитные хабы ФДЦ, 10 в ЮНИКОР</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3853,7 +4029,7 @@
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Входящие лиды LADA в CRM (Новый лид)</t>
+          <t>1. Входящие лиды LADA в CRM (Новый лид)</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -3875,14 +4051,14 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Стабильный органический поток заявок на витрине СберАвто</t>
+          <t>Стабильный органический поток заявок покупателей из региона НН +200 км</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Квалифицированные лиды (Закрепление менеджера)</t>
+          <t>2. Квалифицированные лиды (Закрепление менеджера)</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
@@ -3904,239 +4080,435 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>База клиентов, прошедших скоринг и готовых к покупке</t>
+          <t>База клиентов региона, прошедших скоринг и готовых к покупке</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Всего передано дилерам в НН +200 км (все каналы)</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>3. ПЕРЕДАНО ЛОКАЛЬНЫМ ДИЛЕРАМ В РАДИУСЕ 200 КМ (ФАКТ)</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>527.8</v>
+        <v>700</v>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Доля передачи клиентам дилерам выросла с 5.9% до 42.0%</t>
+          <t>Физические официальные дилерские центры LADA в регионе (АГАТ + ЮНИКОР)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Передано: ЮНИКОР Дзержинск (конкурент)</t>
+          <t xml:space="preserve">  • ГК АГАТ (ЮЛ «Автопрофиль», CRM + MAX)</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>577.8</v>
+        <v>2100</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Основной получатель системного трафика LADA в регионе</t>
+          <t>Нижний Новгород (Московское ш., Родионова) — абсолютный лидер региона!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Передано: ГК АГАТ (ЮЛ «Автопрофиль»)</t>
+          <t xml:space="preserve">  • ЮНИКОР Дзержинск (локальный конкурент)</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>2100</v>
+        <v>233.3</v>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2 лида CRM + 20 цепочек MAX. Существенный рост ручного канала</t>
+          <t>Дзержинск (33 км от НН) — 10 уникальных передач (официальный BI СберАвто)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Передано: Прочим дилерам (в т.ч. межрегион)</t>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>4. УТЕЧКА КЛИЕНТОВ ЗА ПРЕДЕЛЫ 200 КМ (Удаленные кредитные хабы / ФДЦ)</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>275</v>
+        <v>-111</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-86.7</v>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Клиенты с номерами НН, переданные в Техно-Темп, Кан Авто и др.</t>
+          <t>Нижегородские онлайн-заявки, направленные операторами в удаленные центры</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Не передано никому (зависло в CRM / отказ до передачи)</t>
+          <t xml:space="preserve">  • ФДЦ Техно-Темп (Краснодар, ~1 400 км от НН)</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>285</v>
+        <v>93</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-129</v>
+        <v>-81</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>-45.3</v>
+        <v>-87.09999999999999</v>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Резерв для масштабирования прямых передач в АГАТ</t>
+          <t>Удаленный кредитный шлюз СберАвто для онлайн-заявок на автокредит</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>ДОЛЯ АГАТ от фактически переданного трафика</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D13" s="32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>248.2</v>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • ФДЦ Р-Моторс (удаленный кредитный пилот)</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-71.40000000000001</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Каждый 5-й переданный лид в регионе получает АГАТ</t>
+          <t>Удаленный пилот обработки кредитных сделок СберАвто</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>ДОЛЯ АГАТ от квалифицированного спроса региона</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D14" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>2633.3</v>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • КАН АВТО (Казань, ~400 км от НН)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Потенциал роста доли АГАТ — минимум в 3–4 раза (до 30–40%)</t>
+          <t>Заявки клиентов восточных районов области</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Прочим удаленным ДЦ (Боравто Воронеж, Прагматика и др.)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>В августе уходило в Боравто (8), Р-Моторс (7) и др.; в сентябре утечка перекрыта</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>5. НЕ ПЕРЕДАНО ДИЛЕРАМ ОТ ВХОДЯЩИХ ЛИДОВ (баланс: 230 - 49)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>181</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>78.7%</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Остаток входящего спроса без передачи в ДЦ (баланс: 49 передано + 181 = 230)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • в т.ч. квалифицированные клиенты без передачи (269 - 49)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Резерв для масштабирования прямых передач в АГАТ (баланс: 49 + 220 = 269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>ДОЛЯ АГАТ СРЕДИ ЛОКАЛЬНЫХ ДИЛЕРОВ (АГАТ vs ЮНИКОР)</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Среди дилеров области АГАТ забирает 68.8%, опережая ЮНИКОР в 2.2 раза!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>ДОЛЯ АГАТ ОТ ВСЕХ ПЕРЕДАННЫХ КЛИЕНТОВ РЕГИОНА (с учетом утечки)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>5512.5</v>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>44.9%</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Доля АГАТ во всех передачах нижегородцев выросла с 0.8% до 44.9%!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>ДОЛЯ АГАТ ОТ КВАЛИФИЦИРОВАННОГО СПРОСА РЕГИОНА</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>2633.3</v>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Потенциал роста доли АГАТ — минимум в 3–4 раза (до 30–40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>Объем квалифицированного спроса мимо АГАТ, шт</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C21" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D21" s="12" t="n">
         <v>247</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>-55</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>-18.2</v>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>91.8%</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Прямой объем для обсуждения на встрече по открытию слотов</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>* ПОЯСНЕНИЕ ПО ДИЛЕРАМ ДАЛЬШЕ 200 КМ: ДЦ «Техно-Темп» (Краснодар, 1400 км), «Р-Моторс», «КАН АВТО» (Казань, 400 км), «Боравто» (Воронеж, 700 км) и «Прагматика» физически НЕ находятся в радиусе 200 км.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>Они показаны в отчете исключительно как «Межрегиональная утечка»: операторы CRM СберАвто направляли туда заявки нижегородских покупателей (в основном онлайн-автокредиты), вместо отработки на месте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Физически в радиусе 200 км от Нижнего Новгорода работают ТОЛЬКО ДВА официальных дилера LADA: ГК АГАТ (г. Нижний Новгород) и ЮНИКОР (г. Дзержинск, 33 км).</t>
         </is>
       </c>
     </row>
@@ -4151,16 +4523,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="53" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -4198,7 +4570,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Лидов сен, шт</t>
+          <t>Входящие лиды (получено от клиентов), шт</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4208,7 +4580,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Текущий дилер отработки</t>
+          <t>Куда направлен трафик (дилеры отработки)</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -4278,7 +4650,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>ЮНИКОР (Дзержинск) перехватывает 70% данного пояса</t>
+          <t>ЮНИКОР (Дзержинск) получил 10 лидов; АГАТ на Московском ш. идеально доступен для Бора/Балахны</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -4411,19 +4783,34 @@
       <c r="E11" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>ЮНИКОР (65.6%), АГАТ (19.5%), Прочие (14.9%)</t>
+          <t>АГАТ (44.9%), ФДЦ кредитные хабы (32.7%), ЮНИКОР (20.4%), КАН АВТО (2.0%)</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
           <t>Емкость достаточна для удвоения продаж АГАТ LADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>* ПРИМЕЧАНИЕ ПО МЕТОДОЛОГИИ: 133 шт по Нижнему Новгороду (и 230 шт суммарно по радиусу 200 км) — это ВХОДЯЩИЙ ПОТОК (лиды, ПОЛУЧЕННЫЕ от покупателей на витрине СберАвто).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Из них дилерам было ФАКТИЧЕСКИ ОТПРАВЛЕНО 49 лидов: 32 передано локальным дилерам (22 в АГАТ + 10 в ЮНИКОР), а 17 отправлено в удаленные кредитные хабы (Техно-Темп Краснодар и др.). Остальная 181 заявка осталась не переданной дилерам (в работе CRM / отсев скоринга).</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4910,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Lead 001</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>5176812</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>01.09.2026</t>
         </is>
@@ -4551,7 +4938,7 @@
           <t>Автомобиль в наличии на складе</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -4571,17 +4958,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Lead 002</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>5185566</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>02.09.2026</t>
         </is>
@@ -4599,7 +4986,7 @@
           <t>Предложена версия 2026г за 1 225 000 ₽ (+44 тыс)</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -4619,17 +5006,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Lead 003</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>5188560</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>03.09.2026</t>
         </is>
@@ -4647,7 +5034,7 @@
           <t>Согласована скидка СберАвто</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -4667,17 +5054,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Lead 004</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>5204719</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>04.09.2026</t>
         </is>
@@ -4695,7 +5082,7 @@
           <t>Автомобиль подобран</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -4715,17 +5102,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Lead 005</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>5236169</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>08.09.2026</t>
         </is>
@@ -4743,7 +5130,7 @@
           <t>В наличии по спеццене</t>
         </is>
       </c>
-      <c r="H10" s="34" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -4763,17 +5150,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Lead 006</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>5175620</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>09.09.2026</t>
         </is>
@@ -4791,7 +5178,7 @@
           <t>Базовая комплектация Standard</t>
         </is>
       </c>
-      <c r="H11" s="35" t="inlineStr">
+      <c r="H11" s="37" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -4811,17 +5198,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Lead 007</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>5265153</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>11.09.2026</t>
         </is>
@@ -4839,7 +5226,7 @@
           <t>Черный цвет. Предложены варианты дороже, одобрен кредит</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>ПРЕДОПЛАТА</t>
         </is>
@@ -4859,17 +5246,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Lead 008</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>5277735</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>13.09.2026</t>
         </is>
@@ -4887,7 +5274,7 @@
           <t>Подбор комплектации Life</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -4907,17 +5294,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Lead 009</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>5282179</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>14.09.2026</t>
         </is>
@@ -4935,7 +5322,7 @@
           <t>В наличии</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -4955,17 +5342,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Lead 010</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>3246515</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>15.09.2026</t>
         </is>
@@ -4983,7 +5370,7 @@
           <t>Высокий платеж. После пересмотра условий вернулся</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr">
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -5003,17 +5390,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Lead 011</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>3574097</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>16.09.2026</t>
         </is>
@@ -5031,7 +5418,7 @@
           <t>Автомобиль на выдаче</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -5051,17 +5438,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Lead 012</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>5301999</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>17.09.2026</t>
         </is>
@@ -5079,7 +5466,7 @@
           <t>Подготовлен ДКП</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="H17" s="37" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -5099,17 +5486,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>Lead 013</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>5309320</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>18.09.2026</t>
         </is>
@@ -5127,7 +5514,7 @@
           <t>Запрос наличия цвета платина</t>
         </is>
       </c>
-      <c r="H18" s="34" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -5147,17 +5534,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Lead 014</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>5310184</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>19.09.2026</t>
         </is>
@@ -5175,7 +5562,7 @@
           <t>Бюджет до 1 млн</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>ПРЕДОПЛАТА</t>
         </is>
@@ -5195,17 +5582,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Lead 015</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>5338631</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>21.09.2026</t>
         </is>
@@ -5223,7 +5610,7 @@
           <t>В наличии</t>
         </is>
       </c>
-      <c r="H20" s="34" t="inlineStr">
+      <c r="H20" s="36" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -5243,17 +5630,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Lead 016</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>5347349</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>22.09.2026</t>
         </is>
@@ -5271,7 +5658,7 @@
           <t>В наличии</t>
         </is>
       </c>
-      <c r="H21" s="35" t="inlineStr">
+      <c r="H21" s="37" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -5291,17 +5678,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>Lead 017</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>5350112</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>
@@ -5319,7 +5706,7 @@
           <t>Ожидание кредитного специалиста в ДЦ &gt; 1.5 часов</t>
         </is>
       </c>
-      <c r="H22" s="34" t="inlineStr">
+      <c r="H22" s="36" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -5339,17 +5726,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Lead 018</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>5360440</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>
@@ -5367,7 +5754,7 @@
           <t>Трейд-ин BMW (оценка 900к). Клиент не готов доплачивать</t>
         </is>
       </c>
-      <c r="H23" s="35" t="inlineStr">
+      <c r="H23" s="37" t="inlineStr">
         <is>
           <t>ОТКАЗ</t>
         </is>
@@ -5387,17 +5774,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>Lead 019</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>5252935</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>24.09.2026</t>
         </is>
@@ -5415,7 +5802,7 @@
           <t>В наличии</t>
         </is>
       </c>
-      <c r="H24" s="34" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>КУПИЛ</t>
         </is>
@@ -5435,17 +5822,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Lead 020</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>5376045</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>25.09.2026</t>
         </is>
@@ -5463,7 +5850,7 @@
           <t>Запрос актуальности предложения</t>
         </is>
       </c>
-      <c r="H25" s="35" t="inlineStr">
+      <c r="H25" s="37" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
@@ -5572,7 +5959,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>5176812</t>
         </is>
@@ -5587,12 +5974,12 @@
           <t>Сделка закрыта (01.09)</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>ДА (Deal 536756)</t>
         </is>
@@ -5602,7 +5989,7 @@
           <t>Granta (1 150 000 ₽)</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5619,7 +6006,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>5188560</t>
         </is>
@@ -5634,12 +6021,12 @@
           <t>Сделка закрыта (03.09)</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>ДА (Deal 538290)</t>
         </is>
@@ -5649,7 +6036,7 @@
           <t>Granta (1 230 000 ₽)</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5666,7 +6053,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>5236169</t>
         </is>
@@ -5681,12 +6068,12 @@
           <t>Сделка закрыта (08.09)</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>ДА (Deal 550222)</t>
         </is>
@@ -5696,7 +6083,7 @@
           <t>Granta (1 080 000 ₽)</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5713,7 +6100,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>5175620</t>
         </is>
@@ -5728,12 +6115,12 @@
           <t>Сделка закрыта (09.09)</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>ДА (Deal 552410)</t>
         </is>
@@ -5743,7 +6130,7 @@
           <t>Granta (870 000 ₽)</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5760,7 +6147,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>3246515</t>
         </is>
@@ -5775,12 +6162,12 @@
           <t>Сделка закрыта (18.09)</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F10" s="34" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>ДА (Deal 561210)</t>
         </is>
@@ -5790,7 +6177,7 @@
           <t>Vesta (1 584 300 ₽)</t>
         </is>
       </c>
-      <c r="H10" s="34" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5807,7 +6194,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>3574097</t>
         </is>
@@ -5822,12 +6209,12 @@
           <t>Сделка закрыта (19.09)</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>ДА (Deal 562054)</t>
         </is>
@@ -5837,7 +6224,7 @@
           <t>Granta (1 246 000 ₽)</t>
         </is>
       </c>
-      <c r="H11" s="35" t="inlineStr">
+      <c r="H11" s="37" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5854,7 +6241,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>5301999</t>
         </is>
@@ -5869,12 +6256,12 @@
           <t>Сделка закрыта (23.09)</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>ДА (Deal 565516)</t>
         </is>
@@ -5884,7 +6271,7 @@
           <t>Granta (1 108 000 ₽)</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5901,7 +6288,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>5347349</t>
         </is>
@@ -5916,12 +6303,12 @@
           <t>Сделка закрыта (24.09)</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>ДА (Deal 564966)</t>
         </is>
@@ -5931,7 +6318,7 @@
           <t>Granta (1 021 000 ₽)</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5948,7 +6335,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>5252935</t>
         </is>
@@ -5963,12 +6350,12 @@
           <t>Сделка закрыта (25.09)</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>ДА (Deal 567594)</t>
         </is>
@@ -5978,7 +6365,7 @@
           <t>Granta (1 290 000 ₽)</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -5995,7 +6382,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>5265153</t>
         </is>
@@ -6010,12 +6397,12 @@
           <t>Предоплата внесена</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>НЕТ (в процессе)</t>
         </is>
@@ -6025,7 +6412,7 @@
           <t>Granta Comfort (1 071 000 ₽)</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr">
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -6042,7 +6429,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>5310184</t>
         </is>
@@ -6057,12 +6444,12 @@
           <t>Предоплата внесена</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>НЕТ (в процессе)</t>
         </is>
@@ -6072,7 +6459,7 @@
           <t>Granta (997 000 ₽)</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -6089,7 +6476,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>5360440</t>
         </is>
@@ -6104,12 +6491,12 @@
           <t>Отказ дилера</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
@@ -6119,7 +6506,7 @@
           <t>Largus / Trade-in BMW</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="H17" s="37" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -6136,7 +6523,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>5350112</t>
         </is>
@@ -6151,12 +6538,12 @@
           <t>Лид без сделки</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
@@ -6166,7 +6553,7 @@
           <t>Vesta (1 550 000 ₽)</t>
         </is>
       </c>
-      <c r="H18" s="34" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>ТОЧНО СОПОСТАВЛЕН</t>
         </is>
@@ -6275,7 +6662,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Лиды уходят в ЮНИКОР (61) или зависают в CRM из-за отсутствия слотов/кнопки АГАТ</t>
+          <t>220 клиентов не распределены дилерам, 17 ушли в кредитные хабы ФДЦ, 10 в ЮНИКОР</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -6290,7 +6677,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Подключить авто-кнопку CRM для АГАТ Лада и выровнять маршрутизацию с ЮНИКОР</t>
+          <t>Подключить авто-кнопку CRM для АГАТ Лада и перенаправить кредитный трафик</t>
         </is>
       </c>
     </row>
